--- a/data/AttributePool.xlsx
+++ b/data/AttributePool.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,109 +558,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>相性点</t>
+          <t>宝宝属性点</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="H7" t="n">
         <v>30</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>每升一级获得 1 点,五行相性单项上限 50</t>
+          <t>宝宝每升一级获得 5 点,分配到体质/灵力/力量/敏捷</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>仙魔点</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>60</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1500</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>60 级解锁,每级 1 点,仙/魔两路强化</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>宝宝属性点</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>300</v>
-      </c>
-      <c r="H9" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>宝宝每升一级获得 5 点,分配到体质/灵力/力量/敏捷</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
         <v>1</v>
       </c>
     </row>
